--- a/jpcore-r4/fix/issue-1063-coding-terminology/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/fix/issue-1063-coding-terminology/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -865,7 +865,7 @@
     <t>実施されたProcedureのタイプを表すコード。</t>
   </si>
   <si>
-    <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、`Coding`を直接使用して、テキスト、`Coding`、翻訳、および要素間の関係と調整前後の関係を管理するための独自の構造を提供する必要がある。  
+    <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、`Coding`を直接使用して、テキスト、コード、翻訳、および要素間の関係と調整前後の関係を管理するための独自の構造を提供する必要がある。  
 エラーコードなどを記載</t>
   </si>
   <si>

--- a/jpcore-r4/fix/issue-1063-coding-terminology/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/fix/issue-1063-coding-terminology/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -865,7 +865,7 @@
     <t>実施されたProcedureのタイプを表すコード。</t>
   </si>
   <si>
-    <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、`Coding`を直接使用して、テキスト、コード、翻訳、および要素間の関係と調整前後の関係を管理するための独自の構造を提供する必要がある。  
+    <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、`Coding`を直接使用して、テキスト、`Coding`、翻訳、および要素間の関係と調整前後の関係を管理するための独自の構造を提供する必要がある。  
 エラーコードなどを記載</t>
   </si>
   <si>
